--- a/feature/add-pdm/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/add-pdm/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T09:52:41+00:00</t>
+    <t>2026-07-20T09:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/add-pdm/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/add-pdm/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T09:55:54+00:00</t>
+    <t>2026-08-19T09:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/add-pdm/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/add-pdm/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T09:08:02+00:00</t>
+    <t>2026-08-19T10:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
